--- a/KatalonData/EmailTextToPay/BillFileLookUp_Prod.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_Prod.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{E0D9E4F7-8B4B-45A4-8AA3-D32EBB97DEC1}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008C24C3-3705-49A0-8FE0-A523EB089FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
-    <sheet name="BFLU" r:id="rId1" sheetId="1"/>
-    <sheet name="BFLU_1Result" r:id="rId2" sheetId="3"/>
-    <sheet name="BFLUError" r:id="rId3" sheetId="2"/>
+    <sheet name="BFLU" sheetId="1" r:id="rId1"/>
+    <sheet name="BFLU_1Result" sheetId="3" r:id="rId2"/>
+    <sheet name="BFLUError" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="131">
   <si>
     <t>Result</t>
   </si>
@@ -269,87 +269,6 @@
     <t>Patel Companys</t>
   </si>
   <si>
-    <t>Tue Mar 24 18:52:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 18:52:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 18:53:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:00:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:11:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:12:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:13:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:13:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:14:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:14:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:15:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:16:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:16:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:17:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:18:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:18:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:19:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:20:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:20:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:21:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:21:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:22:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:23:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:23:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:24:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:24:58 IST 2026</t>
-  </si>
-  <si>
     <t>Payment app+ 1st + 2nd +3rd lookup</t>
   </si>
   <si>
@@ -365,620 +284,163 @@
     <t>45332116803cA</t>
   </si>
   <si>
-    <t>Thu Apr 23 16:37:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:39:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:40:40 IST 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:44:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:45:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:47:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:47:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:48:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:48:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:49:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:50:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:50:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:51:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:52:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:52:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:53:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:53:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:54:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:55:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:55:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:56:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:56:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:57:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:58:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:58:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:59:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 16:59:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 17:00:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 17:01:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:36:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:37:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:38:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:39:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:39:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:40:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:41:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:41:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:42:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:43:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:44:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:44:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:45:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:46:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:47:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:47:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:48:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:49:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:49:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:50:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:51:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:52:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:53:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:53:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:54:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:55:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:55:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:56:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:57:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:58:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:58:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 09:59:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:00:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:00:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:01:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:02:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:03:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:03:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:04:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:05:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:05:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:06:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:07:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:07:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:08:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:09:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:09:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:10:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:11:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:12:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:12:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:13:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:14:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:14:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:15:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:16:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:16:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:17:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:18:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:18:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:19:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:20:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:20:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:21:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:21:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:22:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:23:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:24:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:25:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:25:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:26:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:27:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:28:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:28:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:29:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:30:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:31:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:31:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:32:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:33:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:33:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:34:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:35:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:35:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:36:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:37:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:38:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:39:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:40:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:41:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:41:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:42:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:43:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:44:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:44:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:45:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:46:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:47:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:48:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:48:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:49:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:50:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:50:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:51:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:52:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:52:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:53:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:54:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:55:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:55:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:56:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:57:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:57:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:58:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:59:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:59:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:00:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:00:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:01:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:02:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:02:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:03:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:04:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:05:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:05:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:06:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:07:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:07:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:08:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 21:03:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 21:04:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 21:22:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 21:23:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 21:30:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 21:31:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 21:37:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 21:37:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 21:55:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 22:00:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 22:09:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 22:10:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 22:46:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 22:47:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 22:48:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 22:59:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:00:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:01:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:34:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:35:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:36:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:36:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:37:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:37:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:38:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:39:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:39:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:40:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:41:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:41:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:42:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:42:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:43:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:43:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:44:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:44:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:45:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:46:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:46:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:47:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:47:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:48:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:49:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:49:45 IST 2026</t>
+    <t>Thu Oct 15 01:01:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:02:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:03:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:03:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:04:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:05:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:06:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:06:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:07:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:08:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:08:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:09:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:10:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:10:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:11:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:12:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:12:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:13:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:14:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:14:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:15:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:16:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:16:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:17:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:22:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:22:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:23:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:24:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:24:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:25:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:27:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:28:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:28:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:29:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:30:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:30:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:31:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:34:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:34:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:35:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:36:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:37:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:37:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 15:38:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 12:38:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 12:39:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 12:39:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 12:40:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 12:41:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 12:41:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 13:08:20 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1037,40 +499,40 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1087,10 +549,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -1125,7 +587,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1177,7 +639,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1288,21 +750,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1319,7 +781,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1391,29 +853,29 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="3" width="11.08984375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="6" width="35.453125" collapsed="true"/>
-    <col min="4" max="4" style="3" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="3" width="24.90625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="3" width="11.26953125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="3" width="9.7265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="3" width="25.6328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="3" width="15.6328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="3" width="13.6328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="7" width="13.54296875" collapsed="true"/>
-    <col min="12" max="16384" style="3" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="32" style="3" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="35.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.7265625" style="3" collapsed="1"/>
+    <col min="5" max="5" width="24.90625" style="3" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="11.26953125" style="3" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="9.7265625" style="3" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="25.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="15.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="13.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="13.54296875" style="7" customWidth="1" collapsed="1"/>
+    <col min="12" max="16384" width="8.7265625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1451,12 +913,12 @@
         <v>62</v>
       </c>
     </row>
-    <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B2" t="s" s="3">
-        <v>284</v>
+    <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>124</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>10</v>
@@ -1471,12 +933,12 @@
         <v>4533213903</v>
       </c>
     </row>
-    <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B3" t="s" s="3">
-        <v>285</v>
+    <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>11</v>
@@ -1491,12 +953,12 @@
         <v>72</v>
       </c>
     </row>
-    <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B4" t="s" s="3">
-        <v>286</v>
+    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
@@ -1511,12 +973,12 @@
         <v>74</v>
       </c>
     </row>
-    <row ht="13" r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B5" t="s" s="3">
-        <v>287</v>
+    <row r="5" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
@@ -1531,12 +993,12 @@
         <v>73</v>
       </c>
     </row>
-    <row ht="13" r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B6" t="s" s="3">
-        <v>288</v>
+    <row r="6" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>55</v>
@@ -1551,12 +1013,12 @@
         <v>12162016223</v>
       </c>
     </row>
-    <row ht="13" r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B7" t="s" s="3">
-        <v>289</v>
+    <row r="7" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>28</v>
@@ -1571,12 +1033,12 @@
         <v>12162016221</v>
       </c>
     </row>
-    <row ht="13" r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B8" t="s" s="3">
-        <v>290</v>
+    <row r="8" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
@@ -1591,12 +1053,12 @@
         <v>12162016222</v>
       </c>
     </row>
-    <row ht="13" r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B9" t="s" s="3">
-        <v>291</v>
+    <row r="9" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>9</v>
@@ -1626,12 +1088,12 @@
         <v>12162016223</v>
       </c>
     </row>
-    <row ht="13" r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B10" t="s" s="3">
-        <v>292</v>
+    <row r="10" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>15</v>
@@ -1649,12 +1111,12 @@
         <v>72</v>
       </c>
     </row>
-    <row ht="13" r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B11" t="s" s="3">
-        <v>293</v>
+    <row r="11" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>14</v>
@@ -1672,12 +1134,12 @@
         <v>73</v>
       </c>
     </row>
-    <row ht="13" r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B12" t="s" s="3">
-        <v>294</v>
+    <row r="12" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>38</v>
@@ -1695,12 +1157,12 @@
         <v>74</v>
       </c>
     </row>
-    <row customHeight="1" ht="18" r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B13" t="s" s="3">
-        <v>295</v>
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>16</v>
@@ -1718,12 +1180,12 @@
         <v>74</v>
       </c>
     </row>
-    <row ht="13" r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B14" t="s" s="3">
-        <v>296</v>
+    <row r="14" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>17</v>
@@ -1741,12 +1203,12 @@
         <v>73</v>
       </c>
     </row>
-    <row customHeight="1" ht="14.5" r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B15" t="s" s="3">
-        <v>297</v>
+    <row r="15" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>30</v>
@@ -1764,12 +1226,12 @@
         <v>12162016221</v>
       </c>
     </row>
-    <row ht="13" r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B16" t="s" s="3">
-        <v>298</v>
+    <row r="16" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>31</v>
@@ -1787,12 +1249,12 @@
         <v>12162016222</v>
       </c>
     </row>
-    <row ht="13" r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B17" t="s" s="3">
-        <v>299</v>
+    <row r="17" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>56</v>
@@ -1810,12 +1272,12 @@
         <v>12162016223</v>
       </c>
     </row>
-    <row ht="13" r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B18" t="s" s="3">
-        <v>300</v>
+    <row r="18" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>32</v>
@@ -1833,12 +1295,12 @@
         <v>12162016221</v>
       </c>
     </row>
-    <row ht="13" r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B19" t="s" s="3">
-        <v>301</v>
+    <row r="19" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>33</v>
@@ -1856,12 +1318,12 @@
         <v>12162016222</v>
       </c>
     </row>
-    <row ht="13" r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B20" t="s" s="3">
-        <v>302</v>
+    <row r="20" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>57</v>
@@ -1879,12 +1341,12 @@
         <v>12162016223</v>
       </c>
     </row>
-    <row ht="25" r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B21" t="s" s="3">
-        <v>303</v>
+    <row r="21" spans="1:11" ht="25" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>54</v>
@@ -1905,12 +1367,12 @@
         <v>12162016223</v>
       </c>
     </row>
-    <row customHeight="1" ht="18" r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B22" t="s" s="3">
-        <v>304</v>
+    <row r="22" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>34</v>
@@ -1928,12 +1390,12 @@
         <v>12162016221</v>
       </c>
     </row>
-    <row ht="13" r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B23" t="s" s="3">
-        <v>305</v>
+    <row r="23" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>35</v>
@@ -1951,12 +1413,12 @@
         <v>12162016222</v>
       </c>
     </row>
-    <row ht="13" r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B24" t="s" s="3">
-        <v>306</v>
+    <row r="24" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>58</v>
@@ -1974,12 +1436,12 @@
         <v>12162016223</v>
       </c>
     </row>
-    <row customHeight="1" ht="17.5" r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B25" t="s" s="3">
-        <v>307</v>
+    <row r="25" spans="1:11" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>36</v>
@@ -1997,12 +1459,12 @@
         <v>12162016221</v>
       </c>
     </row>
-    <row ht="13" r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B26" t="s" s="3">
-        <v>308</v>
+    <row r="26" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>37</v>
@@ -2020,12 +1482,12 @@
         <v>12162016222</v>
       </c>
     </row>
-    <row ht="13" r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B27" t="s" s="3">
-        <v>309</v>
+    <row r="27" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>123</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>59</v>
@@ -2045,28 +1507,28 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A22EE10-F9D4-4571-858C-1BE3B4ED1851}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A22EE10-F9D4-4571-858C-1BE3B4ED1851}">
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="3" width="11.08984375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="6" width="35.453125" collapsed="true"/>
-    <col min="4" max="4" style="3" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="3" width="24.90625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="3" width="14.453125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="3" width="9.7265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="3" width="25.6328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="3" width="15.6328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="3" width="13.6328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="7" width="13.54296875" collapsed="true"/>
-    <col min="12" max="16384" style="3" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="11.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="35.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.7265625" style="3" collapsed="1"/>
+    <col min="5" max="5" width="24.90625" style="3" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.453125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="9.7265625" style="3" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="25.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="15.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="13.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="13.54296875" style="7" customWidth="1" collapsed="1"/>
+    <col min="12" max="16384" width="8.7265625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2104,15 +1566,15 @@
         <v>62</v>
       </c>
     </row>
-    <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B2" t="s" s="3">
-        <v>241</v>
+    <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
@@ -2130,15 +1592,15 @@
         <v>12162016299</v>
       </c>
     </row>
-    <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B3" t="s" s="3">
-        <v>242</v>
-      </c>
-      <c r="C3" t="s" s="6">
-        <v>103</v>
+    <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>4</v>
@@ -2147,18 +1609,18 @@
         <v>71</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B4" t="s" s="3">
-        <v>243</v>
-      </c>
-      <c r="C4" t="s" s="6">
-        <v>104</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
@@ -2167,36 +1629,36 @@
         <v>71</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
   <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="5" width="10.90625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="6" width="30.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="3" width="7.81640625" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="25.1796875" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="3" width="10.81640625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="3" width="9.81640625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="3" width="15.54296875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="3" width="15.6328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="3" width="13.81640625" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="3" width="13.0" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="5" width="45.1796875" collapsed="true"/>
-    <col min="13" max="16384" style="3" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="10.90625" style="5" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="30.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="7.81640625" style="3" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="25.1796875" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="10.81640625" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="9.81640625" style="3" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="15.54296875" style="3" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="15.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="13.81640625" style="3" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="13" style="3" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="45.1796875" style="5" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="8.7265625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="25" r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2234,12 +1696,12 @@
         <v>8</v>
       </c>
     </row>
-    <row ht="13" r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B2" t="s" s="5">
-        <v>244</v>
+    <row r="2" spans="1:12" ht="13" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>20</v>
@@ -2257,12 +1719,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="13" r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B3" t="s" s="5">
-        <v>245</v>
+    <row r="3" spans="1:12" ht="13" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>21</v>
@@ -2280,12 +1742,12 @@
         <v>7</v>
       </c>
     </row>
-    <row customHeight="1" ht="14.5" r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B4" t="s" s="5">
-        <v>246</v>
+    <row r="4" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>22</v>
@@ -2303,12 +1765,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B5" t="s" s="5">
-        <v>247</v>
+    <row r="5" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>23</v>
@@ -2326,12 +1788,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="13" r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B6" t="s" s="5">
-        <v>248</v>
+    <row r="6" spans="1:12" ht="13" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>39</v>
@@ -2349,12 +1811,12 @@
         <v>7</v>
       </c>
     </row>
-    <row customHeight="1" ht="17.5" r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B7" t="s" s="5">
-        <v>249</v>
+    <row r="7" spans="1:12" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>40</v>
@@ -2372,12 +1834,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B8" t="s" s="5">
-        <v>250</v>
+    <row r="8" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>41</v>
@@ -2398,12 +1860,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B9" t="s" s="5">
-        <v>251</v>
+    <row r="9" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>42</v>
@@ -2424,12 +1886,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B10" t="s" s="5">
-        <v>252</v>
+    <row r="10" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>90</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>44</v>
@@ -2450,12 +1912,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B11" t="s" s="5">
-        <v>253</v>
+    <row r="11" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>43</v>
@@ -2476,12 +1938,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B12" t="s" s="5">
-        <v>254</v>
+    <row r="12" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>49</v>
@@ -2502,12 +1964,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B13" t="s" s="5">
-        <v>255</v>
+    <row r="13" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>50</v>
@@ -2528,12 +1990,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B14" t="s" s="5">
-        <v>256</v>
+    <row r="14" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>51</v>
@@ -2554,12 +2016,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B15" t="s" s="5">
-        <v>257</v>
+    <row r="15" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>45</v>
@@ -2580,12 +2042,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B16" t="s" s="5">
-        <v>258</v>
+    <row r="16" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>46</v>
@@ -2606,12 +2068,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B17" t="s" s="5">
-        <v>259</v>
+    <row r="17" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>47</v>
@@ -2632,12 +2094,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B18" t="s" s="5">
-        <v>260</v>
+    <row r="18" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>48</v>
@@ -2658,12 +2120,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B19" t="s" s="5">
-        <v>261</v>
+    <row r="19" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>64</v>
@@ -2681,12 +2143,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B20" t="s" s="5">
-        <v>262</v>
+    <row r="20" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>66</v>
@@ -2707,12 +2169,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B21" t="s" s="5">
-        <v>263</v>
+    <row r="21" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>67</v>
@@ -2733,12 +2195,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B22" t="s" s="5">
-        <v>264</v>
+    <row r="22" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>68</v>
@@ -2759,12 +2221,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="B23" t="s" s="5">
-        <v>265</v>
+    <row r="23" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>69</v>
@@ -2786,7 +2248,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>